--- a/5/search/FY3_Missile3_results/best_solution.xlsx
+++ b/5/search/FY3_Missile3_results/best_solution.xlsx
@@ -490,28 +490,28 @@
         <v>81</v>
       </c>
       <c r="B2" t="n">
-        <v>120.4</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6452.033030180251</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="F2" t="n">
-        <v>-145.9757710162899</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6452.033030180251</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="I2" t="n">
-        <v>-145.9757710162899</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="J2" t="n">
         <v>700</v>
